--- a/src/src/main/resources/template/Budget_Import_Template.xlsx
+++ b/src/src/main/resources/template/Budget_Import_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hc-apm-web\src\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6951F503-2F95-419B-B162-1D3A793C2F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0846A5AD-0D90-4424-99B5-E97647D68914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>申请编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -209,14 +209,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>审核人登录账号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>审核日期(YYYY/MM/DD)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>护士长是否已签名</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -225,14 +217,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>XXXX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>XX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>台</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -241,6 +225,14 @@
   </si>
   <si>
     <t>科室列表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XXX001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>线下审批是否完成</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -360,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -398,9 +390,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -717,45 +706,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AP3"/>
+  <dimension ref="A1:AO3"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="14.1" outlineLevelCol="1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="3" width="8.44921875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.3984375" style="2" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="5" max="5" width="20.34765625" style="9" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="7" width="20.34765625" style="9" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="10" width="8.44921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="7.59765625" customWidth="1"/>
-    <col min="13" max="13" width="7.59765625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="7.59765625" customWidth="1"/>
-    <col min="15" max="15" width="8.44921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.94921875" customWidth="1"/>
-    <col min="17" max="17" width="20.34765625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="24.34765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22.34765625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.3984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="32.25" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="48.1484375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.3984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.44921875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.44921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="8.44921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="7.59765625" customWidth="1"/>
+    <col min="11" max="11" width="7.59765625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="7.59765625" customWidth="1"/>
+    <col min="13" max="13" width="8.44921875" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.94921875" customWidth="1"/>
+    <col min="15" max="15" width="20.34765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.34765625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.34765625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="32.25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="48.1484375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.44921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.44921875" style="3" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.3984375" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.3984375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="16.3984375" customWidth="1"/>
-    <col min="33" max="33" width="26.296875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.44921875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="20.34765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="37" max="39" width="8.59765625" customWidth="1"/>
-    <col min="40" max="41" width="8.59765625" style="3" customWidth="1"/>
-    <col min="42" max="42" width="8.59765625" customWidth="1"/>
+    <col min="30" max="30" width="16.3984375" customWidth="1"/>
+    <col min="31" max="31" width="26.296875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.44921875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="17" customWidth="1"/>
+    <col min="35" max="35" width="20.34765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="36" max="38" width="8.59765625" customWidth="1"/>
+    <col min="39" max="40" width="8.59765625" style="3" customWidth="1"/>
+    <col min="41" max="41" width="8.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" s="7" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:41" s="7" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A1" s="15" t="s">
         <v>37</v>
       </c>
@@ -763,11 +752,11 @@
       <c r="C1" s="16"/>
       <c r="D1" s="16"/>
       <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="12" t="s">
+      <c r="F1" s="12" t="s">
         <v>38</v>
       </c>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
@@ -794,18 +783,17 @@
       <c r="AF1" s="13"/>
       <c r="AG1" s="13"/>
       <c r="AH1" s="13"/>
-      <c r="AI1" s="14"/>
-      <c r="AJ1" s="12" t="s">
+      <c r="AI1" s="12" t="s">
         <v>39</v>
       </c>
+      <c r="AJ1" s="13"/>
       <c r="AK1" s="13"/>
       <c r="AL1" s="13"/>
       <c r="AM1" s="13"/>
       <c r="AN1" s="13"/>
-      <c r="AO1" s="13"/>
-      <c r="AP1" s="14"/>
+      <c r="AO1" s="14"/>
     </row>
-    <row r="2" spans="1:42" s="1" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:41" s="1" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -821,195 +809,164 @@
       <c r="E2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="AE2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI2" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AJ2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO2" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.5">
+      <c r="A3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AH2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AI2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AJ2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="AK2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AL2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AM2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="AO2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="AP2" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.5">
-      <c r="C3" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E3" s="9">
         <v>45292</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="9">
-        <v>45292</v>
+        <v>43</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
+      </c>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="3">
+        <v>1</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M3" s="3">
-        <v>1</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="3">
         <v>100</v>
       </c>
-      <c r="AE3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ3" s="9">
-        <v>45301</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AN3" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO3" s="3">
-        <v>100</v>
-      </c>
-      <c r="AP3" t="s">
+      <c r="AC3" t="s">
         <v>45</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="H1:AI1"/>
-    <mergeCell ref="AJ1:AP1"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="F1:AH1"/>
+    <mergeCell ref="AI1:AO1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576" xr:uid="{20276040-B9A9-4644-AF37-CB91BE871FB4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576" xr:uid="{20276040-B9A9-4644-AF37-CB91BE871FB4}">
       <formula1>"拨款资金,横向专项经费(科研),自筹资金"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AD2:AE1048576 AG2:AH1048576 AF1:AF1048576" xr:uid="{022E29AA-A658-4335-B807-32F40AF2CA85}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576 AB2:AC1048576 AD1:AD1048576 AE2:AF1048576 AH1:AH1048576" xr:uid="{022E29AA-A658-4335-B807-32F40AF2CA85}">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1041,11 +998,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A1" s="10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/src/main/resources/template/Budget_Import_Template.xlsx
+++ b/src/src/main/resources/template/Budget_Import_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Java Codes\company\hc-apm-web\src\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2DD47B-66CF-4D42-A4DD-75FCC6AAEF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C298613-5FC4-4EEE-BFDB-EFF159457471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11895" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -668,7 +668,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -737,12 +737,6 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -755,6 +749,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -768,15 +771,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1223,37 +1217,37 @@
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
       <c r="E2" s="27"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="29" t="s">
+      <c r="F2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="30"/>
-      <c r="AH2" s="31"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="29"/>
       <c r="AI2" s="22" t="s">
         <v>4</v>
       </c>
@@ -1426,8 +1420,8 @@
   <mergeCells count="4">
     <mergeCell ref="AI2:AQ2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:AH2"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F2:AH2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3 KF2 UB2 ADX2 ANT2 AXP2 BHL2 BRH2 CBD2 CKZ2 CUV2 DER2 DON2 DYJ2 EIF2 ESB2 FBX2 FLT2 FVP2 GFL2 GPH2 GZD2 HIZ2 HSV2 ICR2 IMN2 IWJ2 JGF2 JQB2 JZX2 KJT2 KTP2 LDL2 LNH2 LXD2 MGZ2 MQV2 NAR2 NKN2 NUJ2 OEF2 OOB2 OXX2 PHT2 PRP2 QBL2 QLH2 QVD2 REZ2 ROV2 RYR2 SIN2 SSJ2 TCF2 TMB2 TVX2 UFT2 UPP2 UZL2 VJH2 VTD2 WCZ2 WMV2 WWR2 WWL3 WWN2 WMP3 WMR2 WCT3 WCV2 VSX3 VSZ2 VJB3 VJD2 UZF3 UZH2 UPJ3 UPL2 UFN3 UFP2 TVR3 TVT2 TLV3 TLX2 TBZ3 TCB2 SSD3 SSF2 SIH3 SIJ2 RYL3 RYN2 ROP3 ROR2 RET3 REV2 QUX3 QUZ2 QLB3 QLD2 QBF3 QBH2 PRJ3 PRL2 PHN3 PHP2 OXR3 OXT2 ONV3 ONX2 ODZ3 OEB2 NUD3 NUF2 NKH3 NKJ2 NAL3 NAN2 MQP3 MQR2 MGT3 MGV2 LWX3 LWZ2 LNB3 LND2 LDF3 LDH2 KTJ3 KTL2 KJN3 KJP2 JZR3 JZT2 JPV3 JPX2 JFZ3 JGB2 IWD3 IWF2 IMH3 IMJ2 ICL3 ICN2 HSP3 HSR2 HIT3 HIV2 GYX3 GYZ2 GPB3 GPD2 GFF3 GFH2 FVJ3 FVL2 FLN3 FLP2 FBR3 FBT2 ERV3 ERX2 EHZ3 EIB2 DYD3 DYF2 DOH3 DOJ2 DEL3 DEN2 CUP3 CUR2 CKT3 CKV2 CAX3 CAZ2 BRB3 BRD2 BHF3 BHH2 AXJ3 AXL2 ANN3 ANP2 ADR3 ADT2 TV3 TX2 JZ3 KB2 R4:R1048576 AC4:AG1048576" xr:uid="{13F3CE03-28C9-49F3-BBCD-48C9321A8AE1}">
@@ -1453,633 +1447,633 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="12" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
     </row>
     <row r="2" spans="1:7" ht="12" customHeight="1">
       <c r="A2" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
     </row>
     <row r="3" spans="1:7" ht="12" customHeight="1">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
     </row>
     <row r="4" spans="1:7" ht="12" customHeight="1">
       <c r="A4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
     </row>
     <row r="5" spans="1:7" ht="12" customHeight="1">
       <c r="A5" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
     </row>
     <row r="6" spans="1:7" ht="12" customHeight="1">
       <c r="A6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7" spans="1:7" ht="12" customHeight="1">
       <c r="A7" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:7" ht="12" customHeight="1">
       <c r="A8" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
     </row>
     <row r="9" spans="1:7" ht="12" customHeight="1">
       <c r="A9" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
     </row>
     <row r="10" spans="1:7" ht="12" customHeight="1">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
     </row>
     <row r="11" spans="1:7" ht="12" customHeight="1">
       <c r="A11" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
     </row>
     <row r="12" spans="1:7" ht="12" customHeight="1">
       <c r="A12" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
     </row>
     <row r="13" spans="1:7" ht="12" customHeight="1">
       <c r="A13" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
     </row>
     <row r="14" spans="1:7" ht="12" customHeight="1">
       <c r="A14" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
     </row>
     <row r="15" spans="1:7" ht="12" customHeight="1">
       <c r="A15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
     </row>
     <row r="16" spans="1:7" ht="12" customHeight="1">
       <c r="A16" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
     </row>
     <row r="17" spans="1:7" ht="12" customHeight="1">
       <c r="A17" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
     </row>
     <row r="18" spans="1:7" ht="12" customHeight="1">
       <c r="A18" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
     </row>
     <row r="19" spans="1:7" ht="12" customHeight="1">
       <c r="A19" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
     </row>
     <row r="20" spans="1:7" ht="12" customHeight="1">
       <c r="A20" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
     </row>
     <row r="21" spans="1:7" ht="12" customHeight="1">
       <c r="A21" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
     </row>
     <row r="22" spans="1:7" ht="12" customHeight="1">
       <c r="A22" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
     </row>
     <row r="23" spans="1:7" ht="12" customHeight="1">
       <c r="A23" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
     </row>
     <row r="24" spans="1:7" ht="12" customHeight="1">
       <c r="A24" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="B24" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
     </row>
     <row r="25" spans="1:7" ht="12" customHeight="1">
       <c r="A25" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
     </row>
     <row r="26" spans="1:7" ht="12" customHeight="1">
       <c r="A26" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
     </row>
     <row r="27" spans="1:7" ht="12" customHeight="1">
       <c r="A27" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="32" t="s">
+      <c r="B27" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
     </row>
     <row r="28" spans="1:7" ht="12" customHeight="1">
       <c r="A28" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
     </row>
     <row r="29" spans="1:7" ht="12" customHeight="1">
       <c r="A29" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
     </row>
     <row r="30" spans="1:7" ht="12" customHeight="1">
       <c r="A30" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
     </row>
     <row r="31" spans="1:7" ht="12" customHeight="1">
       <c r="A31" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
     </row>
     <row r="32" spans="1:7" ht="12" customHeight="1">
       <c r="A32" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
     </row>
     <row r="33" spans="1:7" ht="12" customHeight="1">
       <c r="A33" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="32" t="s">
+      <c r="B33" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
     </row>
     <row r="34" spans="1:7" ht="12" customHeight="1">
       <c r="A34" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="32" t="s">
+      <c r="B34" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
     </row>
     <row r="35" spans="1:7" ht="12" customHeight="1">
       <c r="A35" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="32" t="s">
+      <c r="B35" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="33"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
     </row>
     <row r="36" spans="1:7" ht="12" customHeight="1">
       <c r="A36" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="32" t="s">
+      <c r="B36" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
     </row>
     <row r="37" spans="1:7" ht="12" customHeight="1">
       <c r="A37" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="32" t="s">
+      <c r="B37" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
     </row>
     <row r="38" spans="1:7" ht="12" customHeight="1">
       <c r="A38" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="32" t="s">
+      <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
     </row>
     <row r="39" spans="1:7" ht="12" customHeight="1">
       <c r="A39" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="33"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
     </row>
     <row r="40" spans="1:7" ht="12" customHeight="1">
       <c r="A40" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="32" t="s">
+      <c r="B40" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="33"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
     </row>
     <row r="41" spans="1:7" ht="12" customHeight="1">
-      <c r="A41" s="39" t="s">
+      <c r="A41" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="40"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="41"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="34"/>
     </row>
     <row r="42" spans="1:7" ht="12" customHeight="1">
       <c r="A42" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B42" s="32" t="s">
+      <c r="B42" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
     </row>
     <row r="43" spans="1:7" ht="12" customHeight="1">
       <c r="A43" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="32" t="s">
+      <c r="B43" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
     </row>
     <row r="44" spans="1:7" ht="12" customHeight="1">
       <c r="A44" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="32" t="s">
+      <c r="B44" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="C44" s="33"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
     </row>
     <row r="45" spans="1:7" ht="12" customHeight="1">
       <c r="A45" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="32" t="s">
+      <c r="B45" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
     </row>
     <row r="46" spans="1:7" ht="12" customHeight="1">
       <c r="A46" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="32" t="s">
+      <c r="B46" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="33"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="33"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
     </row>
     <row r="47" spans="1:7" ht="12" customHeight="1">
       <c r="A47" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="32" t="s">
+      <c r="B47" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="33"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="33"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
     </row>
     <row r="48" spans="1:7" ht="12" customHeight="1">
       <c r="A48" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="32" t="s">
+      <c r="B48" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="33"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="33"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
     </row>
     <row r="49" spans="1:7" ht="12" customHeight="1">
       <c r="A49" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="32" t="s">
+      <c r="B49" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="33"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="33"/>
-      <c r="F49" s="33"/>
-      <c r="G49" s="33"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
     </row>
     <row r="50" spans="1:7" ht="12" customHeight="1"/>
     <row r="51" spans="1:7" ht="12" customHeight="1"/>
@@ -2161,30 +2155,15 @@
     <row r="127" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="B49:G49"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="B42:G42"/>
-    <mergeCell ref="B43:G43"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B47:G47"/>
-    <mergeCell ref="B48:G48"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="B22:G22"/>
@@ -2201,15 +2180,30 @@
     <mergeCell ref="B21:G21"/>
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="B48:G48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
